--- a/src/main/resources/INPUT/link/links_BP23_A_ref.xlsx
+++ b/src/main/resources/INPUT/link/links_BP23_A_ref.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="39">
   <si>
     <t xml:space="preserve">2030-2031</t>
   </si>
@@ -69,49 +69,10 @@
     <t xml:space="preserve">Forced_Outage_HVAC</t>
   </si>
   <si>
-    <t xml:space="preserve">AT-CH</t>
+    <t xml:space="preserve">AT-BE</t>
   </si>
   <si>
     <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT-DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT-ITn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-FR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-LU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-NL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-UKgb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH-DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH-FR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH-Itn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ-DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ-PL</t>
   </si>
   <si>
     <t xml:space="preserve">Itcn-Itn</t>
@@ -405,538 +366,122 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>7500</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>3400</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>4800</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>4300</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>4800</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>3700</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>3700</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>4050</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>4050</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>4050</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>2600</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G16" s="0"/>
@@ -1283,12 +828,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>4500</v>
@@ -1329,7 +874,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>300</v>
@@ -1370,7 +915,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -1411,7 +956,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3100</v>
@@ -1452,7 +997,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>720</v>
@@ -1493,7 +1038,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1000</v>
@@ -1534,7 +1079,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>2000</v>
@@ -1575,7 +1120,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1000</v>
@@ -1616,7 +1161,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>700</v>
@@ -1657,7 +1202,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1000</v>
@@ -1698,7 +1243,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1300</v>
@@ -1739,7 +1284,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1400</v>
@@ -1780,7 +1325,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>600</v>
@@ -1821,7 +1366,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>700</v>
@@ -1862,7 +1407,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>250</v>
@@ -1903,7 +1448,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>2145</v>
@@ -1944,7 +1489,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1400</v>
@@ -1985,7 +1530,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>600</v>
@@ -2026,7 +1571,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>3300</v>
@@ -2067,7 +1612,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>8100</v>
@@ -2108,7 +1653,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>6800</v>
@@ -2149,7 +1694,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>450</v>

--- a/src/main/resources/INPUT/link/links_BP23_A_ref.xlsx
+++ b/src/main/resources/INPUT/link/links_BP23_A_ref.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="40">
   <si>
     <t xml:space="preserve">2030-2031</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t xml:space="preserve">FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT-BZ</t>
   </si>
   <si>
     <t xml:space="preserve">Itcn-Itn</t>
@@ -262,8 +265,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -367,13 +370,45 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
@@ -814,8 +849,8 @@
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -828,12 +863,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>4500</v>
@@ -874,7 +909,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>300</v>
@@ -915,7 +950,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -956,7 +991,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3100</v>
@@ -997,7 +1032,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>720</v>
@@ -1038,7 +1073,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1000</v>
@@ -1079,7 +1114,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>2000</v>
@@ -1120,7 +1155,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1000</v>
@@ -1161,7 +1196,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>700</v>
@@ -1202,7 +1237,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1000</v>
@@ -1243,7 +1278,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1300</v>
@@ -1284,7 +1319,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1400</v>
@@ -1325,7 +1360,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>600</v>
@@ -1366,7 +1401,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>700</v>
@@ -1407,7 +1442,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>250</v>
@@ -1448,7 +1483,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>2145</v>
@@ -1489,7 +1524,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1400</v>
@@ -1530,7 +1565,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>600</v>
@@ -1571,7 +1606,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>3300</v>
@@ -1612,7 +1647,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>8100</v>
@@ -1653,7 +1688,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>6800</v>
@@ -1694,7 +1729,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>450</v>
@@ -1787,7 +1822,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
